--- a/ig/ch-epl/CodeSystem-ch-epl-foph-gamme.xlsx
+++ b/ig/ch-epl/CodeSystem-ch-epl-foph-gamme.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T12:35:50+00:00</t>
+    <t>2026-04-07T14:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>16</t>
   </si>
   <si>
     <t>Level</t>
@@ -153,67 +153,91 @@
     <t>756002004002</t>
   </si>
   <si>
+    <t>Oral prolonged-release</t>
+  </si>
+  <si>
+    <t>756002004003</t>
+  </si>
+  <si>
+    <t>Oral liquid</t>
+  </si>
+  <si>
+    <t>756002004004</t>
+  </si>
+  <si>
     <t>Parenteral</t>
   </si>
   <si>
-    <t>756002004003</t>
-  </si>
-  <si>
-    <t>Oral liquid</t>
-  </si>
-  <si>
-    <t>756002004004</t>
-  </si>
-  <si>
-    <t>Oral prolonged-release</t>
-  </si>
-  <si>
     <t>756002004005</t>
   </si>
   <si>
+    <t>Parenteral depot</t>
+  </si>
+  <si>
+    <t>756002004006</t>
+  </si>
+  <si>
+    <t>Inhalation</t>
+  </si>
+  <si>
+    <t>756002004007</t>
+  </si>
+  <si>
+    <t>Topical</t>
+  </si>
+  <si>
+    <t>756002004008</t>
+  </si>
+  <si>
+    <t>Topical wash</t>
+  </si>
+  <si>
+    <t>756002004009</t>
+  </si>
+  <si>
+    <t>Ophthalmic</t>
+  </si>
+  <si>
+    <t>756002004010</t>
+  </si>
+  <si>
+    <t>Auricular</t>
+  </si>
+  <si>
+    <t>756002004011</t>
+  </si>
+  <si>
+    <t>Nasal</t>
+  </si>
+  <si>
+    <t>756002004012</t>
+  </si>
+  <si>
+    <t>Transdermal</t>
+  </si>
+  <si>
+    <t>756002004013</t>
+  </si>
+  <si>
     <t>Rectal Vaginal</t>
   </si>
   <si>
-    <t>756002004006</t>
-  </si>
-  <si>
-    <t>Topical</t>
-  </si>
-  <si>
-    <t>756002004007</t>
-  </si>
-  <si>
-    <t>Topical wash</t>
-  </si>
-  <si>
-    <t>756002004008</t>
-  </si>
-  <si>
-    <t>Nasal</t>
-  </si>
-  <si>
-    <t>756002004009</t>
-  </si>
-  <si>
-    <t>Parenteral depot</t>
-  </si>
-  <si>
-    <t>756002004010</t>
-  </si>
-  <si>
-    <t>Inhalation</t>
-  </si>
-  <si>
-    <t>756002004011</t>
-  </si>
-  <si>
-    <t>Transdermal</t>
-  </si>
-  <si>
-    <t>756002004012</t>
-  </si>
-  <si>
-    <t>Ophthalmic</t>
+    <t>756002004014</t>
+  </si>
+  <si>
+    <t>Topical oral</t>
+  </si>
+  <si>
+    <t>756002004015</t>
+  </si>
+  <si>
+    <t>Therapy devices for administering medicinal products</t>
+  </si>
+  <si>
+    <t>756002004016</t>
+  </si>
+  <si>
+    <t>Special nutrition</t>
   </si>
 </sst>
 </file>
@@ -525,7 +549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -686,6 +710,54 @@
       </c>
       <c r="D13" s="2"/>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
